--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E7402B1-A355-4E44-A824-EB11A47B17BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92B7C3A-FE90-4EDA-962A-4FB2D778A384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39160" yWindow="760" windowWidth="28800" windowHeight="15910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40680" yWindow="2280" windowWidth="28800" windowHeight="15910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Date</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>Preparation GitHub, Folder Structure, Templates</t>
+  </si>
+  <si>
+    <t>Template project proposal, meetings + communication</t>
   </si>
 </sst>
 </file>
@@ -372,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" customWidth="1"/>
@@ -406,7 +409,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -418,6 +421,17 @@
       </c>
       <c r="C3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/130a09d975ce9163/Documents/GitHub/wu_dslab_infrared-city/timesheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92B7C3A-FE90-4EDA-962A-4FB2D778A384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{E92B7C3A-FE90-4EDA-962A-4FB2D778A384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{980B0FF3-74AE-4A8B-B0D0-1496C902965B}"/>
   <bookViews>
-    <workbookView xWindow="40680" yWindow="2280" windowWidth="28800" windowHeight="15910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="15466" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="10">
   <si>
     <t>Date</t>
   </si>
@@ -57,6 +57,15 @@
   </si>
   <si>
     <t>Template project proposal, meetings + communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>meetings</t>
+  </si>
+  <si>
+    <t>create second teams and regular meetings and communication</t>
   </si>
 </sst>
 </file>
@@ -375,15 +384,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H72"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="13.26953125" customWidth="1"/>
-    <col min="2" max="2" width="59.26953125" customWidth="1"/>
-    <col min="8" max="8" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.29296875" customWidth="1"/>
+    <col min="2" max="2" width="59.29296875" customWidth="1"/>
+    <col min="8" max="8" width="9.87890625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -397,7 +406,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A2" s="1">
         <v>46090</v>
       </c>
@@ -409,10 +418,10 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A3" s="1">
         <v>46090</v>
       </c>
@@ -423,7 +432,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A4" s="1">
         <v>46091</v>
       </c>
@@ -432,6 +441,358 @@
       </c>
       <c r="C4">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A5" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A6" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A11" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A12" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A13" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A14" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A15" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A16" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A17" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A18" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A19" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A20" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A21" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A22" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A23" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A24" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A25" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A26" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A27" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A28" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A29" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A30" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A31" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A32" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A33" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A34" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A35" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A36" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A37" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A38" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A39" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A40" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A41" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A42" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A43" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A44" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A45" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A46" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A47" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A48" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A49" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A50" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A51" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A52" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A53" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A54" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A55" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A56" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A57" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A58" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A59" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A60" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A61" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A62" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A63" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A64" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A65" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A66" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A67" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A68" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A69" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A70" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A71" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A72" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/130a09d975ce9163/Documents/GitHub/wu_dslab_infrared-city/timesheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{E92B7C3A-FE90-4EDA-962A-4FB2D778A384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{980B0FF3-74AE-4A8B-B0D0-1496C902965B}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{E92B7C3A-FE90-4EDA-962A-4FB2D778A384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FC3E6A1-1B84-4F4E-BE6A-F569D4E8A3DD}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="15466" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="11">
   <si>
     <t>Date</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>create second teams and regular meetings and communication</t>
+  </si>
+  <si>
+    <t>write first version of communication and teams in project proposal</t>
   </si>
 </sst>
 </file>
@@ -119,6 +122,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -418,7 +425,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>9.75</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.5">
@@ -466,8 +473,14 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
+      <c r="A7" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>1.5</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.5">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/130a09d975ce9163/Documents/GitHub/wu_dslab_infrared-city/timesheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{E92B7C3A-FE90-4EDA-962A-4FB2D778A384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FC3E6A1-1B84-4F4E-BE6A-F569D4E8A3DD}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{E92B7C3A-FE90-4EDA-962A-4FB2D778A384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC6623AB-50FD-4951-9CD5-C22FD4874931}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="15466" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="12">
   <si>
     <t>Date</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>write first version of communication and teams in project proposal</t>
+  </si>
+  <si>
+    <t>add bibtex, rewrite literature, search new literature</t>
   </si>
 </sst>
 </file>
@@ -425,7 +428,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>11.25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.5">
@@ -484,8 +487,14 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
+      <c r="A8" s="1">
+        <v>46096</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8">
+        <v>0.75</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.5">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/130a09d975ce9163/Documents/GitHub/wu_dslab_infrared-city/timesheets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{E92B7C3A-FE90-4EDA-962A-4FB2D778A384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC6623AB-50FD-4951-9CD5-C22FD4874931}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF24A34-F3BC-4027-9655-D02C13E7C294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="15466" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40680" yWindow="2280" windowWidth="28800" windowHeight="15910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="13">
   <si>
     <t>Date</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>add bibtex, rewrite literature, search new literature</t>
+  </si>
+  <si>
+    <t>meeting + followup of meeting</t>
   </si>
 </sst>
 </file>
@@ -125,10 +128,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -395,14 +394,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H72"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.29296875" customWidth="1"/>
-    <col min="2" max="2" width="59.29296875" customWidth="1"/>
-    <col min="8" max="8" width="9.87890625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.26953125" customWidth="1"/>
+    <col min="2" max="2" width="59.26953125" customWidth="1"/>
+    <col min="8" max="8" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -416,7 +415,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>46090</v>
       </c>
@@ -428,10 +427,10 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>46090</v>
       </c>
@@ -442,7 +441,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>46091</v>
       </c>
@@ -453,7 +452,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>46094</v>
       </c>
@@ -464,7 +463,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>46094</v>
       </c>
@@ -475,7 +474,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>46095</v>
       </c>
@@ -486,7 +485,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>46096</v>
       </c>
@@ -497,322 +496,328 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>46096</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>7</v>
       </c>

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF24A34-F3BC-4027-9655-D02C13E7C294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D466C4-807C-47D1-A189-83E91F28C04C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40680" yWindow="2280" windowWidth="28800" windowHeight="15910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="14">
   <si>
     <t>Date</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>meeting + followup of meeting</t>
+  </si>
+  <si>
+    <t>order server</t>
   </si>
 </sst>
 </file>
@@ -427,7 +430,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>14</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -508,8 +511,14 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>7</v>
+      <c r="A10" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10">
+        <v>0.25</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D466C4-807C-47D1-A189-83E91F28C04C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{365275AE-8E32-40D9-84AB-5BC6F5D9C205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40680" yWindow="2280" windowWidth="28800" windowHeight="15910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="15">
   <si>
     <t>Date</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>order server</t>
+  </si>
+  <si>
+    <t>improve project plan</t>
   </si>
 </sst>
 </file>
@@ -430,7 +433,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>14.25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -522,8 +525,14 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>7</v>
+      <c r="A11" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11">
+        <v>0.75</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{365275AE-8E32-40D9-84AB-5BC6F5D9C205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9498A7-D1B2-4A41-8C4D-AF523C616ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40680" yWindow="2280" windowWidth="28800" windowHeight="15910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="16">
   <si>
     <t>Date</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>improve project plan</t>
+  </si>
+  <si>
+    <t>abgabe project plan</t>
   </si>
 </sst>
 </file>
@@ -433,7 +436,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>15</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -536,8 +539,14 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
-        <v>7</v>
+      <c r="A12" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12">
+        <v>0.25</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9498A7-D1B2-4A41-8C4D-AF523C616ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB79110-3CED-4B42-B9F6-09212C7DA357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40680" yWindow="2280" windowWidth="28800" windowHeight="15910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>abgabe project plan</t>
+  </si>
+  <si>
+    <t>meeting, nächste schritte planen, protokoll schreiben, coaches zwischenstand</t>
   </si>
 </sst>
 </file>
@@ -406,7 +409,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" customWidth="1"/>
-    <col min="2" max="2" width="59.26953125" customWidth="1"/>
+    <col min="2" max="2" width="71.54296875" customWidth="1"/>
     <col min="8" max="8" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -436,7 +439,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>15.25</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -535,7 +538,7 @@
         <v>14</v>
       </c>
       <c r="C11">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -550,8 +553,14 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
-        <v>7</v>
+      <c r="A13" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13">
+        <v>1.25</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB79110-3CED-4B42-B9F6-09212C7DA357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926B4DBF-9C5F-454D-85BD-0358299CF3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40680" yWindow="2280" windowWidth="28800" windowHeight="15910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="18">
   <si>
     <t>Date</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>meeting, nächste schritte planen, protokoll schreiben, coaches zwischenstand</t>
+  </si>
+  <si>
+    <t>setup own access to jupyter</t>
   </si>
 </sst>
 </file>
@@ -439,7 +442,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>16.75</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -564,8 +567,14 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
-        <v>7</v>
+      <c r="A14" s="1">
+        <v>46102</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14">
+        <v>0.5</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926B4DBF-9C5F-454D-85BD-0358299CF3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2238D2CE-5A41-4F53-949C-67B889CCA7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40680" yWindow="2280" windowWidth="28800" windowHeight="15910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -442,7 +442,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>17.25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -574,7 +574,7 @@
         <v>17</v>
       </c>
       <c r="C14">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2238D2CE-5A41-4F53-949C-67B889CCA7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5545BB1B-9AB1-421A-AC03-B4EC948A54FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40680" yWindow="2280" windowWidth="28800" windowHeight="15910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="44680" yWindow="3060" windowWidth="28760" windowHeight="15910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="19">
   <si>
     <t>Date</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>setup own access to jupyter</t>
+  </si>
+  <si>
+    <t>meeting: feedback project plan</t>
   </si>
 </sst>
 </file>
@@ -442,7 +445,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>17</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -578,8 +581,14 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
-        <v>7</v>
+      <c r="A15" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15">
+        <v>0.5</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5545BB1B-9AB1-421A-AC03-B4EC948A54FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A5A531F-A616-4995-8B15-53DD7F82D501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="44680" yWindow="3060" windowWidth="28760" windowHeight="15910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="20">
   <si>
     <t>Date</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>meeting: feedback project plan</t>
+  </si>
+  <si>
+    <t>project plan with timeplan in github</t>
   </si>
 </sst>
 </file>
@@ -445,7 +448,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>17.5</v>
+        <v>22.75</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -588,12 +591,18 @@
         <v>18</v>
       </c>
       <c r="C15">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
-        <v>7</v>
+      <c r="A16" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A5A531F-A616-4995-8B15-53DD7F82D501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC49606-6141-48C9-BFA5-A64157313A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="44680" yWindow="3060" windowWidth="28760" windowHeight="15910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="21">
   <si>
     <t>Date</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>project plan with timeplan in github</t>
+  </si>
+  <si>
+    <t>meeting, project plan, gantt, task assignment, weekly report to data coaches</t>
   </si>
 </sst>
 </file>
@@ -448,7 +451,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>22.75</v>
+        <v>25.25</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -605,82 +608,88 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>7</v>
       </c>

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC49606-6141-48C9-BFA5-A64157313A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB5C65E-ECB6-479A-964B-188E2353846E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="44680" yWindow="3060" windowWidth="28760" windowHeight="15910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="22">
   <si>
     <t>Date</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>meeting, project plan, gantt, task assignment, weekly report to data coaches</t>
+  </si>
+  <si>
+    <t>feedback in refined project plan for organization, timeplan chapters. Export github gantt</t>
   </si>
 </sst>
 </file>
@@ -451,7 +454,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>25.25</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -620,8 +623,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
-        <v>7</v>
+      <c r="A18" s="1">
+        <v>46109</v>
+      </c>
+      <c r="B18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18">
+        <v>2.25</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB5C65E-ECB6-479A-964B-188E2353846E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC14458-6BBE-422F-A8CC-72B27DB60FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44680" yWindow="3060" windowWidth="28760" windowHeight="15910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="23">
   <si>
     <t>Date</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>feedback in refined project plan for organization, timeplan chapters. Export github gantt</t>
+  </si>
+  <si>
+    <t>final prepare of refined project plan and hand in. Close tickets</t>
   </si>
 </sst>
 </file>
@@ -454,7 +457,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>27.5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -634,8 +637,14 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
-        <v>7</v>
+      <c r="A19" s="1">
+        <v>46110</v>
+      </c>
+      <c r="B19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19">
+        <v>0.5</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC14458-6BBE-422F-A8CC-72B27DB60FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3594B57B-80C9-4081-9B4D-BCC4A894BAA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="3420" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="24">
   <si>
     <t>Date</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>final prepare of refined project plan and hand in. Close tickets</t>
+  </si>
+  <si>
+    <t>start finding of dates for sparring meeting</t>
   </si>
 </sst>
 </file>
@@ -457,7 +460,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>28</v>
+        <v>28.25</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -648,8 +651,14 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
-        <v>7</v>
+      <c r="A20" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20">
+        <v>0.25</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3594B57B-80C9-4081-9B4D-BCC4A894BAA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F99C9B-D208-495A-99DA-5DA4B8F6C1A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="41160" yWindow="1310" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="25">
   <si>
     <t>Date</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>start finding of dates for sparring meeting</t>
+  </si>
+  <si>
+    <t>think about chapters in report, create template for report and slides</t>
   </si>
 </sst>
 </file>
@@ -460,7 +463,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>28.25</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -662,8 +665,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
-        <v>7</v>
+      <c r="A21" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F99C9B-D208-495A-99DA-5DA4B8F6C1A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717358F8-3261-4D7C-86AA-A3BB65ED0115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="41160" yWindow="1310" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="26">
   <si>
     <t>Date</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>think about chapters in report, create template for report and slides</t>
+  </si>
+  <si>
+    <t>subtickets and planning of report and presentation + prepare agenda for tomorrow</t>
   </si>
 </sst>
 </file>
@@ -463,7 +466,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>31.25</v>
+        <v>32.25</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -676,8 +679,14 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
-        <v>7</v>
+      <c r="A22" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717358F8-3261-4D7C-86AA-A3BB65ED0115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B070A9E-05AD-47B3-B1FD-B4C4D920F1DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41160" yWindow="1310" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5530" yWindow="1990" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="32">
   <si>
     <t>Date</t>
   </si>
@@ -114,6 +114,24 @@
   </si>
   <si>
     <t>subtickets and planning of report and presentation + prepare agenda for tomorrow</t>
+  </si>
+  <si>
+    <t>weekly meeting in team + direct followup</t>
+  </si>
+  <si>
+    <t>Need</t>
+  </si>
+  <si>
+    <t>Open Weeks</t>
+  </si>
+  <si>
+    <t>End Datum</t>
+  </si>
+  <si>
+    <t>Need Hours</t>
+  </si>
+  <si>
+    <t>Need per week</t>
   </si>
 </sst>
 </file>
@@ -149,9 +167,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -432,15 +452,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:R72"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" customWidth="1"/>
     <col min="2" max="2" width="71.54296875" customWidth="1"/>
     <col min="8" max="8" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -453,8 +474,14 @@
       <c r="H1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="Q1" t="s">
+        <v>29</v>
+      </c>
+      <c r="R1" s="2">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>46090</v>
       </c>
@@ -466,10 +493,16 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>32.25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>34.75</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>46090</v>
       </c>
@@ -479,8 +512,15 @@
       <c r="C3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="Q3" t="s">
+        <v>28</v>
+      </c>
+      <c r="R3" s="3">
+        <f ca="1">(R1 - TODAY()) / 7</f>
+        <v>11.428571428571429</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>46091</v>
       </c>
@@ -491,7 +531,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>46094</v>
       </c>
@@ -501,8 +541,15 @@
       <c r="C5">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="Q5" t="s">
+        <v>30</v>
+      </c>
+      <c r="R5">
+        <f>R2-H2</f>
+        <v>85.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>46094</v>
       </c>
@@ -512,8 +559,15 @@
       <c r="C6">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="Q6" t="s">
+        <v>31</v>
+      </c>
+      <c r="R6">
+        <f ca="1">R5/R3</f>
+        <v>7.4593749999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>46095</v>
       </c>
@@ -524,7 +578,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>46096</v>
       </c>
@@ -535,7 +589,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>46096</v>
       </c>
@@ -546,7 +600,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>46097</v>
       </c>
@@ -557,7 +611,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>46097</v>
       </c>
@@ -568,7 +622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>46099</v>
       </c>
@@ -579,7 +633,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>46100</v>
       </c>
@@ -590,7 +644,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>46102</v>
       </c>
@@ -601,7 +655,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>46104</v>
       </c>
@@ -612,7 +666,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>46106</v>
       </c>
@@ -690,8 +744,14 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
-        <v>7</v>
+      <c r="A23" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23">
+        <v>2.5</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
@@ -941,5 +1001,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B070A9E-05AD-47B3-B1FD-B4C4D920F1DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44CF8565-0075-425E-BAAB-E33F26475105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5530" yWindow="1990" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="33">
   <si>
     <t>Date</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>Need per week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">meeting with </t>
   </si>
 </sst>
 </file>
@@ -493,7 +496,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>34.75</v>
+        <v>35.5</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -517,7 +520,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>11.428571428571429</v>
+        <v>10.857142857142858</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -546,7 +549,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>85.25</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -564,7 +567,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>7.4593749999999996</v>
+        <v>7.7828947368421053</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -755,8 +758,14 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
-        <v>7</v>
+      <c r="A24" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24">
+        <v>0.75</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44CF8565-0075-425E-BAAB-E33F26475105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A0864D-19E9-4E8D-91A9-AF65E54C506F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5530" yWindow="1990" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="34">
   <si>
     <t>Date</t>
   </si>
@@ -135,6 +135,9 @@
   </si>
   <si>
     <t xml:space="preserve">meeting with </t>
+  </si>
+  <si>
+    <t>gespräch moritz</t>
   </si>
 </sst>
 </file>
@@ -496,7 +499,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>35.5</v>
+        <v>36</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -549,7 +552,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>84.5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -567,7 +570,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>7.7828947368421053</v>
+        <v>7.7368421052631575</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -769,8 +772,14 @@
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
-        <v>7</v>
+      <c r="A25" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25">
+        <v>0.5</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A0864D-19E9-4E8D-91A9-AF65E54C506F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97038DAD-E3DF-4C0A-8982-162E526DB5BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5530" yWindow="1990" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="35">
   <si>
     <t>Date</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>gespräch moritz</t>
+  </si>
+  <si>
+    <t>meeting, nachbereitung (einladungen aussenden, git aufräumen,...)</t>
   </si>
 </sst>
 </file>
@@ -499,7 +502,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>36</v>
+        <v>37.5</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -523,7 +526,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>10.857142857142858</v>
+        <v>10.285714285714286</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -552,7 +555,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>84</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -570,7 +573,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>7.7368421052631575</v>
+        <v>8.0208333333333321</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -783,8 +786,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
-        <v>7</v>
+      <c r="A26" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26">
+        <v>1.5</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97038DAD-E3DF-4C0A-8982-162E526DB5BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B0AE56-FDBB-43AD-A8C7-3F73D19B0DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="36">
   <si>
     <t>Date</t>
   </si>
@@ -141,6 +141,9 @@
   </si>
   <si>
     <t>meeting, nachbereitung (einladungen aussenden, git aufräumen,...)</t>
+  </si>
+  <si>
+    <t>weekly report to data coaches</t>
   </si>
 </sst>
 </file>
@@ -502,7 +505,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -555,7 +558,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>82.5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -573,7 +576,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>8.0208333333333321</v>
+        <v>7.9722222222222214</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -797,8 +800,14 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
-        <v>7</v>
+      <c r="A27" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27">
+        <v>0.5</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B0AE56-FDBB-43AD-A8C7-3F73D19B0DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC7AC031-5E68-42F4-AF8E-AC69F0C36B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="38">
   <si>
     <t>Date</t>
   </si>
@@ -144,6 +144,12 @@
   </si>
   <si>
     <t>weekly report to data coaches</t>
+  </si>
+  <si>
+    <t>report</t>
+  </si>
+  <si>
+    <t>slides</t>
   </si>
 </sst>
 </file>
@@ -505,7 +511,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>38</v>
+        <v>43.25</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -529,7 +535,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>10.285714285714286</v>
+        <v>10.142857142857142</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -558,7 +564,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>82</v>
+        <v>76.75</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -576,7 +582,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>7.9722222222222214</v>
+        <v>7.5669014084507049</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -811,13 +817,25 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
-        <v>7</v>
+      <c r="A28" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B28" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28">
+        <v>3.25</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
-        <v>7</v>
+      <c r="A29" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC7AC031-5E68-42F4-AF8E-AC69F0C36B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC790188-CC3E-4B33-BCEF-22565D2EAF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="40">
   <si>
     <t>Date</t>
   </si>
@@ -150,6 +150,12 @@
   </si>
   <si>
     <t>slides</t>
+  </si>
+  <si>
+    <t>meeting report+slides</t>
+  </si>
+  <si>
+    <t>meeting mit betreuer + slides meeting</t>
   </si>
 </sst>
 </file>
@@ -511,7 +517,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>43.25</v>
+        <v>45</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -535,7 +541,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>10.142857142857142</v>
+        <v>9.8571428571428577</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -564,7 +570,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>76.75</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -582,7 +588,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>7.5669014084507049</v>
+        <v>7.6086956521739131</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -839,13 +845,25 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
-        <v>7</v>
+      <c r="A30" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30">
+        <v>0.75</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="1" t="s">
-        <v>7</v>
+      <c r="A31" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC790188-CC3E-4B33-BCEF-22565D2EAF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08DC746D-3FFF-4CBC-8A51-ED67D3E394B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="41">
   <si>
     <t>Date</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t>meeting mit betreuer + slides meeting</t>
+  </si>
+  <si>
+    <t>cleanup report</t>
   </si>
 </sst>
 </file>
@@ -517,7 +520,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>45</v>
+        <v>45.5</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -570,7 +573,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>75</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -588,7 +591,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>7.6086956521739131</v>
+        <v>7.557971014492753</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -867,8 +870,14 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="1" t="s">
-        <v>7</v>
+      <c r="A32" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B32" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32">
+        <v>0.5</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08DC746D-3FFF-4CBC-8A51-ED67D3E394B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11CDB77C-7E3F-45E0-AADD-780E97083D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="43">
   <si>
     <t>Date</t>
   </si>
@@ -159,6 +159,12 @@
   </si>
   <si>
     <t>cleanup report</t>
+  </si>
+  <si>
+    <t>prepare handin intermediate</t>
+  </si>
+  <si>
+    <t>prepare presentation - my part - what to say exactly</t>
   </si>
 </sst>
 </file>
@@ -520,7 +526,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>45.5</v>
+        <v>50.25</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -544,7 +550,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>9.8571428571428577</v>
+        <v>9.7142857142857135</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -573,7 +579,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>74.5</v>
+        <v>69.75</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -591,7 +597,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>7.557971014492753</v>
+        <v>7.1801470588235299</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -880,82 +886,94 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A33" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B33" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B34" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>7</v>
       </c>

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11CDB77C-7E3F-45E0-AADD-780E97083D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E57816B-A09E-4EAF-AFC7-A8AF89B98107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="44">
   <si>
     <t>Date</t>
   </si>
@@ -165,6 +165,9 @@
   </si>
   <si>
     <t>prepare presentation - my part - what to say exactly</t>
+  </si>
+  <si>
+    <t>intermed presentation</t>
   </si>
 </sst>
 </file>
@@ -526,7 +529,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>50.25</v>
+        <v>51.5</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -550,7 +553,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>9.7142857142857135</v>
+        <v>9.5714285714285712</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -579,7 +582,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>69.75</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -597,7 +600,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>7.1801470588235299</v>
+        <v>7.1567164179104479</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -909,8 +912,14 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="1" t="s">
-        <v>7</v>
+      <c r="A35" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35">
+        <v>1.25</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E57816B-A09E-4EAF-AFC7-A8AF89B98107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FEE8B2D-2F94-43BE-ABBE-DA6E0D196D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="45">
   <si>
     <t>Date</t>
   </si>
@@ -168,6 +168,9 @@
   </si>
   <si>
     <t>intermed presentation</t>
+  </si>
+  <si>
+    <t>short discussion with team, creation of tickets regarding feedback, send weekly report to data coaches</t>
   </si>
 </sst>
 </file>
@@ -529,7 +532,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>51.5</v>
+        <v>54</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -553,7 +556,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>9.5714285714285712</v>
+        <v>9.4285714285714288</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -582,7 +585,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>68.5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -600,7 +603,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>7.1567164179104479</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -923,8 +926,14 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="1" t="s">
-        <v>7</v>
+      <c r="A36" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B36" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36">
+        <v>2.5</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FEE8B2D-2F94-43BE-ABBE-DA6E0D196D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E590DD-AD26-46DE-A0C0-960DA2E45904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="46">
   <si>
     <t>Date</t>
   </si>
@@ -171,6 +171,9 @@
   </si>
   <si>
     <t>short discussion with team, creation of tickets regarding feedback, send weekly report to data coaches</t>
+  </si>
+  <si>
+    <t>weekly meeting + writing of protocoll and preparation for meeting</t>
   </si>
 </sst>
 </file>
@@ -532,7 +535,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>54</v>
+        <v>55.25</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -556,7 +559,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>9.4285714285714288</v>
+        <v>8.4285714285714288</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -585,7 +588,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>66</v>
+        <v>64.75</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -603,7 +606,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>7</v>
+        <v>7.6822033898305087</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -937,8 +940,14 @@
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="1" t="s">
-        <v>7</v>
+      <c r="A37" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B37" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37">
+        <v>1.25</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E590DD-AD26-46DE-A0C0-960DA2E45904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{371F9539-8512-43B7-9516-B826531C1268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="47">
   <si>
     <t>Date</t>
   </si>
@@ -174,6 +174,9 @@
   </si>
   <si>
     <t>weekly meeting + writing of protocoll and preparation for meeting</t>
+  </si>
+  <si>
+    <t>sparring group meeting</t>
   </si>
 </sst>
 </file>
@@ -535,7 +538,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>55.25</v>
+        <v>56.25</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -559,7 +562,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>8.4285714285714288</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -588,7 +591,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>64.75</v>
+        <v>63.75</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -606,7 +609,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>7.6822033898305087</v>
+        <v>7.96875</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -951,8 +954,14 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="1" t="s">
-        <v>7</v>
+      <c r="A38" s="1">
+        <v>46145</v>
+      </c>
+      <c r="B38" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{371F9539-8512-43B7-9516-B826531C1268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BEA1E8B-29BC-4ADD-BD23-F7056D430438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="48">
   <si>
     <t>Date</t>
   </si>
@@ -177,6 +177,9 @@
   </si>
   <si>
     <t>sparring group meeting</t>
+  </si>
+  <si>
+    <t>invite data coaches</t>
   </si>
 </sst>
 </file>
@@ -538,7 +541,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>56.25</v>
+        <v>56.75</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -591,7 +594,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>63.75</v>
+        <v>63.25</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -609,7 +612,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>7.96875</v>
+        <v>7.90625</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -965,8 +968,14 @@
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="1" t="s">
-        <v>7</v>
+      <c r="A39" s="1">
+        <v>46145</v>
+      </c>
+      <c r="B39" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39">
+        <v>0.5</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BEA1E8B-29BC-4ADD-BD23-F7056D430438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2A2B72-E2CD-476A-A6F0-7276F2A7D10C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="49">
   <si>
     <t>Date</t>
   </si>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>invite data coaches</t>
+  </si>
+  <si>
+    <t>weekly</t>
   </si>
 </sst>
 </file>
@@ -541,7 +544,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>56.75</v>
+        <v>57.25</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -565,7 +568,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>8</v>
+        <v>7.4285714285714288</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -594,7 +597,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>63.25</v>
+        <v>62.75</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -612,7 +615,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>7.90625</v>
+        <v>8.447115384615385</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -979,8 +982,14 @@
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="1" t="s">
-        <v>7</v>
+      <c r="A40" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B40" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40">
+        <v>0.5</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2A2B72-E2CD-476A-A6F0-7276F2A7D10C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A82635-8CA0-4B10-BB69-07CABCFD5874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="50">
   <si>
     <t>Date</t>
   </si>
@@ -183,6 +183,9 @@
   </si>
   <si>
     <t>weekly</t>
+  </si>
+  <si>
+    <t>recreate model from literature  M. Freudenberg, S. Schnell, and P. Magdon, “A sentinel-2 machine learning dataset for tree species classification in germany,</t>
   </si>
 </sst>
 </file>
@@ -544,7 +547,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>57.25</v>
+        <v>62.75</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -568,7 +571,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>7.4285714285714288</v>
+        <v>7.1428571428571432</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -597,7 +600,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>62.75</v>
+        <v>57.25</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -615,7 +618,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>8.447115384615385</v>
+        <v>8.0149999999999988</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -993,8 +996,14 @@
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="1" t="s">
-        <v>7</v>
+      <c r="A41" s="1">
+        <v>46151</v>
+      </c>
+      <c r="B41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41">
+        <v>5.5</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A82635-8CA0-4B10-BB69-07CABCFD5874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA61530B-810F-47C3-A8BD-832DB758031C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
   <si>
     <t>Date</t>
   </si>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t>recreate model from literature  M. Freudenberg, S. Schnell, and P. Magdon, “A sentinel-2 machine learning dataset for tree species classification in germany,</t>
+  </si>
+  <si>
+    <t>upload and create from reference literature</t>
   </si>
 </sst>
 </file>
@@ -547,7 +550,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>62.75</v>
+        <v>65.25</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -571,7 +574,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>7.1428571428571432</v>
+        <v>6.8571428571428568</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -600,7 +603,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>57.25</v>
+        <v>54.75</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -618,7 +621,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>8.0149999999999988</v>
+        <v>7.984375</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -1007,8 +1010,14 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="1" t="s">
-        <v>7</v>
+      <c r="A42" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B42" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42">
+        <v>2.5</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA61530B-810F-47C3-A8BD-832DB758031C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9CC3B7-3C40-45D4-9085-923790654D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="52">
   <si>
     <t>Date</t>
   </si>
@@ -189,6 +189,9 @@
   </si>
   <si>
     <t>upload and create from reference literature</t>
+  </si>
+  <si>
+    <t>weekly meeting</t>
   </si>
 </sst>
 </file>
@@ -550,7 +553,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>65.25</v>
+        <v>65.5</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -574,7 +577,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>6.8571428571428568</v>
+        <v>6.4285714285714288</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -603,7 +606,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>54.75</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -621,7 +624,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>7.984375</v>
+        <v>8.4777777777777779</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -1021,8 +1024,14 @@
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="1" t="s">
-        <v>7</v>
+      <c r="A43" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43">
+        <v>0.25</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9CC3B7-3C40-45D4-9085-923790654D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E284A13C-5A92-4908-A444-E319A2191150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="53">
   <si>
     <t>Date</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>weekly meeting</t>
+  </si>
+  <si>
+    <t>plan model</t>
   </si>
 </sst>
 </file>
@@ -553,7 +556,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>65.5</v>
+        <v>67.5</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -577,7 +580,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>6.4285714285714288</v>
+        <v>5.7142857142857144</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -606,7 +609,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>54.5</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -624,7 +627,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>8.4777777777777779</v>
+        <v>9.1875</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -1035,8 +1038,14 @@
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="1" t="s">
-        <v>7</v>
+      <c r="A44" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B44" t="s">
+        <v>52</v>
+      </c>
+      <c r="C44">
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E284A13C-5A92-4908-A444-E319A2191150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8A12E5-F497-4898-A1D3-919436DC11A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="54">
   <si>
     <t>Date</t>
   </si>
@@ -195,6 +195,9 @@
   </si>
   <si>
     <t>plan model</t>
+  </si>
+  <si>
+    <t>weekly + preparation + nachher</t>
   </si>
 </sst>
 </file>
@@ -556,7 +559,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>67.5</v>
+        <v>68.5</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -580,7 +583,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>5.7142857142857144</v>
+        <v>5.4285714285714288</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -609,7 +612,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>52.5</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -627,7 +630,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>9.1875</v>
+        <v>9.4868421052631575</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -1049,8 +1052,14 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="1" t="s">
-        <v>7</v>
+      <c r="A45" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8A12E5-F497-4898-A1D3-919436DC11A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD914DAB-CA6F-4086-B95C-A32117C0D73C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
   <si>
     <t>Date</t>
   </si>
@@ -198,6 +198,15 @@
   </si>
   <si>
     <t>weekly + preparation + nachher</t>
+  </si>
+  <si>
+    <t>future work research</t>
+  </si>
+  <si>
+    <t>future work write</t>
+  </si>
+  <si>
+    <t>furture work write</t>
   </si>
 </sst>
 </file>
@@ -559,7 +568,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>68.5</v>
+        <v>75.5</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -583,7 +592,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>5.4285714285714288</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -612,7 +621,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>51.5</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -630,7 +639,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>9.4868421052631575</v>
+        <v>9.734375</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -1063,18 +1072,36 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="1" t="s">
-        <v>7</v>
+      <c r="A46" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B46" t="s">
+        <v>54</v>
+      </c>
+      <c r="C46">
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="1" t="s">
-        <v>7</v>
+      <c r="A47" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B47" t="s">
+        <v>55</v>
+      </c>
+      <c r="C47">
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" s="1" t="s">
-        <v>7</v>
+      <c r="A48" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B48" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD914DAB-CA6F-4086-B95C-A32117C0D73C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91FC397-C629-4C2D-93B0-48E520D36428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="58">
   <si>
     <t>Date</t>
   </si>
@@ -207,6 +207,9 @@
   </si>
   <si>
     <t>furture work write</t>
+  </si>
+  <si>
+    <t>weekly + vor und nachbereitung</t>
   </si>
 </sst>
 </file>
@@ -568,7 +571,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>75.5</v>
+        <v>77</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -592,7 +595,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>4.5714285714285712</v>
+        <v>4.4285714285714288</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -621,7 +624,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>44.5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -639,7 +642,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>9.734375</v>
+        <v>9.7096774193548381</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -1104,82 +1107,88 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A49" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B49" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>7</v>
       </c>

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91FC397-C629-4C2D-93B0-48E520D36428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2196A5F8-B7EF-4DAB-8AF1-62D8665BA147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="59">
   <si>
     <t>Date</t>
   </si>
@@ -210,6 +210,9 @@
   </si>
   <si>
     <t>weekly + vor und nachbereitung</t>
+  </si>
+  <si>
+    <t>presentation slides</t>
   </si>
 </sst>
 </file>
@@ -571,7 +574,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -595,7 +598,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>4.4285714285714288</v>
+        <v>4.1428571428571432</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -624,7 +627,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -642,7 +645,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>9.7096774193548381</v>
+        <v>10.137931034482758</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -1119,8 +1122,14 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" s="1" t="s">
-        <v>7</v>
+      <c r="A50" s="1">
+        <v>46172</v>
+      </c>
+      <c r="B50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2196A5F8-B7EF-4DAB-8AF1-62D8665BA147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C7B316-800A-49FC-9A54-63EDB7A022D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
   <si>
     <t>Date</t>
   </si>
@@ -213,6 +213,9 @@
   </si>
   <si>
     <t>presentation slides</t>
+  </si>
+  <si>
+    <t>make repo public</t>
   </si>
 </sst>
 </file>
@@ -574,7 +577,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>78</v>
+        <v>78.75</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -627,7 +630,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>42</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -645,7 +648,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>10.137931034482758</v>
+        <v>9.956896551724137</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -1133,8 +1136,14 @@
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" s="1" t="s">
-        <v>7</v>
+      <c r="A51" s="1">
+        <v>46172</v>
+      </c>
+      <c r="B51" t="s">
+        <v>59</v>
+      </c>
+      <c r="C51">
+        <v>0.75</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C7B316-800A-49FC-9A54-63EDB7A022D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F29C737-F24D-4347-AA3E-D9745CA57767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="62">
   <si>
     <t>Date</t>
   </si>
@@ -216,6 +216,12 @@
   </si>
   <si>
     <t>make repo public</t>
+  </si>
+  <si>
+    <t>discussion</t>
+  </si>
+  <si>
+    <t>discussion + conclucion+ abstract</t>
   </si>
 </sst>
 </file>
@@ -577,7 +583,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>78.75</v>
+        <v>89.75</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -601,7 +607,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>4.1428571428571432</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -630,7 +636,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>41.25</v>
+        <v>30.25</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -648,7 +654,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>9.956896551724137</v>
+        <v>7.5625</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -1147,13 +1153,25 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" s="1" t="s">
-        <v>7</v>
+      <c r="A52" s="1">
+        <v>46172</v>
+      </c>
+      <c r="B52" t="s">
+        <v>60</v>
+      </c>
+      <c r="C52">
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="1" t="s">
-        <v>7</v>
+      <c r="A53" s="1">
+        <v>46173</v>
+      </c>
+      <c r="B53" t="s">
+        <v>61</v>
+      </c>
+      <c r="C53">
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F29C737-F24D-4347-AA3E-D9745CA57767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{985E7BA7-8E7E-4B54-A132-EA96455FF885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -583,7 +583,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>89.75</v>
+        <v>85.75</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -636,7 +636,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>30.25</v>
+        <v>34.25</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -654,7 +654,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>7.5625</v>
+        <v>8.5625</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -1160,7 +1160,7 @@
         <v>60</v>
       </c>
       <c r="C52">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
@@ -1171,7 +1171,7 @@
         <v>61</v>
       </c>
       <c r="C53">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{985E7BA7-8E7E-4B54-A132-EA96455FF885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F658655A-7563-4C85-8BED-02C866296E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="64">
   <si>
     <t>Date</t>
   </si>
@@ -222,6 +222,12 @@
   </si>
   <si>
     <t>discussion + conclucion+ abstract</t>
+  </si>
+  <si>
+    <t>meeting mit betreuer + nachbesprechung</t>
+  </si>
+  <si>
+    <t>update slides</t>
   </si>
 </sst>
 </file>
@@ -583,7 +589,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>85.75</v>
+        <v>87.5</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -607,7 +613,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>4</v>
+        <v>3.4285714285714284</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -636,7 +642,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>34.25</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -654,7 +660,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>8.5625</v>
+        <v>9.4791666666666679</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -1175,13 +1181,25 @@
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" s="1" t="s">
-        <v>7</v>
+      <c r="A54" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B54" t="s">
+        <v>62</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" s="1" t="s">
-        <v>7</v>
+      <c r="A55" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B55" t="s">
+        <v>63</v>
+      </c>
+      <c r="C55">
+        <v>0.75</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F658655A-7563-4C85-8BED-02C866296E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0047ECF8-0798-4A2A-97C7-8673880CB31C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="65">
   <si>
     <t>Date</t>
   </si>
@@ -228,6 +228,9 @@
   </si>
   <si>
     <t>update slides</t>
+  </si>
+  <si>
+    <t>abgabe draft final</t>
   </si>
 </sst>
 </file>
@@ -589,7 +592,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>87.5</v>
+        <v>89</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
@@ -613,7 +616,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>3.4285714285714284</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -642,7 +645,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>32.5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -660,7 +663,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>9.4791666666666679</v>
+        <v>10.333333333333334</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -1203,13 +1206,14 @@
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" s="1" t="s">
-        <v>7</v>
+      <c r="A56" s="1">
+        <v>46180</v>
+      </c>
+      <c r="B56" t="s">
+        <v>64</v>
+      </c>
+      <c r="C56">
+        <v>1.5</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0047ECF8-0798-4A2A-97C7-8673880CB31C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D744EA3F-C07F-4A18-9779-E925F041AD94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>Date</t>
   </si>
@@ -59,9 +59,6 @@
     <t>Template project proposal, meetings + communication</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>meetings</t>
   </si>
   <si>
@@ -231,6 +228,9 @@
   </si>
   <si>
     <t>abgabe draft final</t>
+  </si>
+  <si>
+    <t>meeting, slides check</t>
   </si>
 </sst>
 </file>
@@ -551,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R72"/>
+  <dimension ref="A1:R76"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" customWidth="1"/>
@@ -574,7 +574,7 @@
         <v>4</v>
       </c>
       <c r="Q1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R1" s="2">
         <v>46201</v>
@@ -592,10 +592,10 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R2">
         <v>120</v>
@@ -612,11 +612,11 @@
         <v>2</v>
       </c>
       <c r="Q3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>3</v>
+        <v>2.4285714285714284</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -635,17 +635,17 @@
         <v>46094</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>1.5</v>
       </c>
       <c r="Q5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -653,17 +653,17 @@
         <v>46094</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6">
         <v>0.75</v>
       </c>
       <c r="Q6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>10.333333333333334</v>
+        <v>12.352941176470589</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -671,7 +671,7 @@
         <v>46095</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7">
         <v>1.5</v>
@@ -682,7 +682,7 @@
         <v>46096</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8">
         <v>0.75</v>
@@ -693,7 +693,7 @@
         <v>46096</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -704,7 +704,7 @@
         <v>46097</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10">
         <v>0.25</v>
@@ -715,7 +715,7 @@
         <v>46097</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -726,7 +726,7 @@
         <v>46099</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>0.25</v>
@@ -737,7 +737,7 @@
         <v>46100</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>1.25</v>
@@ -748,7 +748,7 @@
         <v>46102</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>0.25</v>
@@ -759,7 +759,7 @@
         <v>46104</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>0.75</v>
@@ -770,7 +770,7 @@
         <v>46106</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -781,7 +781,7 @@
         <v>46107</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>2.5</v>
@@ -792,7 +792,7 @@
         <v>46109</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>2.25</v>
@@ -803,7 +803,7 @@
         <v>46110</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>0.5</v>
@@ -814,7 +814,7 @@
         <v>46111</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>0.25</v>
@@ -825,7 +825,7 @@
         <v>46118</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>3</v>
@@ -836,7 +836,7 @@
         <v>46120</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -847,7 +847,7 @@
         <v>46121</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>2.5</v>
@@ -858,7 +858,7 @@
         <v>46125</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C24">
         <v>0.75</v>
@@ -869,7 +869,7 @@
         <v>46125</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C25">
         <v>0.5</v>
@@ -880,7 +880,7 @@
         <v>46128</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26">
         <v>1.5</v>
@@ -891,7 +891,7 @@
         <v>46129</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C27">
         <v>0.5</v>
@@ -902,7 +902,7 @@
         <v>46130</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C28">
         <v>3.25</v>
@@ -913,7 +913,7 @@
         <v>46130</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -924,7 +924,7 @@
         <v>46131</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30">
         <v>0.75</v>
@@ -935,7 +935,7 @@
         <v>46132</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -946,7 +946,7 @@
         <v>46132</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C32">
         <v>0.5</v>
@@ -957,7 +957,7 @@
         <v>46133</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C33">
         <v>3.25</v>
@@ -968,7 +968,7 @@
         <v>46133</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C34">
         <v>1.5</v>
@@ -979,7 +979,7 @@
         <v>46134</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C35">
         <v>1.25</v>
@@ -990,7 +990,7 @@
         <v>46135</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C36">
         <v>2.5</v>
@@ -1001,7 +1001,7 @@
         <v>46142</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C37">
         <v>1.25</v>
@@ -1012,7 +1012,7 @@
         <v>46145</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -1023,7 +1023,7 @@
         <v>46145</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C39">
         <v>0.5</v>
@@ -1034,7 +1034,7 @@
         <v>46149</v>
       </c>
       <c r="B40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C40">
         <v>0.5</v>
@@ -1045,7 +1045,7 @@
         <v>46151</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C41">
         <v>5.5</v>
@@ -1056,7 +1056,7 @@
         <v>46153</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C42">
         <v>2.5</v>
@@ -1067,7 +1067,7 @@
         <v>46156</v>
       </c>
       <c r="B43" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C43">
         <v>0.25</v>
@@ -1078,7 +1078,7 @@
         <v>46161</v>
       </c>
       <c r="B44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C44">
         <v>2</v>
@@ -1089,7 +1089,7 @@
         <v>46163</v>
       </c>
       <c r="B45" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -1100,7 +1100,7 @@
         <v>46167</v>
       </c>
       <c r="B46" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46">
         <v>2</v>
@@ -1111,7 +1111,7 @@
         <v>46168</v>
       </c>
       <c r="B47" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C47">
         <v>3</v>
@@ -1122,7 +1122,7 @@
         <v>46169</v>
       </c>
       <c r="B48" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C48">
         <v>2</v>
@@ -1133,7 +1133,7 @@
         <v>46170</v>
       </c>
       <c r="B49" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C49">
         <v>1.5</v>
@@ -1144,7 +1144,7 @@
         <v>46172</v>
       </c>
       <c r="B50" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>46172</v>
       </c>
       <c r="B51" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C51">
         <v>0.75</v>
@@ -1166,7 +1166,7 @@
         <v>46172</v>
       </c>
       <c r="B52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C52">
         <v>3</v>
@@ -1177,7 +1177,7 @@
         <v>46173</v>
       </c>
       <c r="B53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C53">
         <v>4</v>
@@ -1188,7 +1188,7 @@
         <v>46174</v>
       </c>
       <c r="B54" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -1199,7 +1199,7 @@
         <v>46177</v>
       </c>
       <c r="B55" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C55">
         <v>0.75</v>
@@ -1210,86 +1210,79 @@
         <v>46180</v>
       </c>
       <c r="B56" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C56">
         <v>1.5</v>
       </c>
     </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B57" t="s">
+        <v>64</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+    </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A58" s="1"/>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A59" s="1"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A60" s="1"/>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A61" s="1"/>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A62" s="1"/>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A63" s="1"/>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A64" s="1"/>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A65" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A65" s="1"/>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A66" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A66" s="1"/>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A67" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A67" s="1"/>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A68" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A68" s="1"/>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A69" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A69" s="1"/>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A70" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A70" s="1"/>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A71" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A71" s="1"/>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A72" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A72" s="1"/>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A73" s="1"/>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A74" s="1"/>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A75" s="1"/>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A76" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D744EA3F-C07F-4A18-9779-E925F041AD94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2317E65-1866-43D4-AAF6-322140360981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>Date</t>
   </si>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>meeting, slides check</t>
+  </si>
+  <si>
+    <t>introduction, abstract, rel work rework</t>
   </si>
 </sst>
 </file>
@@ -592,7 +595,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="Q2" t="s">
         <v>26</v>
@@ -616,7 +619,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>2.4285714285714284</v>
+        <v>2.1428571428571428</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -645,7 +648,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -663,7 +666,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>12.352941176470589</v>
+        <v>12.133333333333333</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -1228,7 +1231,15 @@
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" s="1"/>
+      <c r="A58" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B58" t="s">
+        <v>65</v>
+      </c>
+      <c r="C58">
+        <v>4</v>
+      </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2317E65-1866-43D4-AAF6-322140360981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F0211B-C089-4E7A-9621-864809CB0FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t>Date</t>
   </si>
@@ -234,6 +234,9 @@
   </si>
   <si>
     <t>introduction, abstract, rel work rework</t>
+  </si>
+  <si>
+    <t>meeting with sparing gorup</t>
   </si>
 </sst>
 </file>
@@ -595,7 +598,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q2" t="s">
         <v>26</v>
@@ -619,7 +622,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>2.1428571428571428</v>
+        <v>1.5714285714285714</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -648,7 +651,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -666,7 +669,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>12.133333333333333</v>
+        <v>15.90909090909091</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -1242,7 +1245,15 @@
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" s="1"/>
+      <c r="A59" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B59" t="s">
+        <v>66</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="1"/>

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F0211B-C089-4E7A-9621-864809CB0FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3DA6D0E-44DF-4F2B-A160-00EF4EB062B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>Date</t>
   </si>
@@ -237,6 +237,12 @@
   </si>
   <si>
     <t>meeting with sparing gorup</t>
+  </si>
+  <si>
+    <t>vorbereitung präsentation</t>
+  </si>
+  <si>
+    <t>final präsentation</t>
   </si>
 </sst>
 </file>
@@ -598,7 +604,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="Q2" t="s">
         <v>26</v>
@@ -651,7 +657,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -669,7 +675,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>15.90909090909091</v>
+        <v>9.545454545454545</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -1256,10 +1262,26 @@
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" s="1"/>
+      <c r="A60" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B60" t="s">
+        <v>67</v>
+      </c>
+      <c r="C60">
+        <v>3</v>
+      </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" s="1"/>
+      <c r="A61" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B61" t="s">
+        <v>68</v>
+      </c>
+      <c r="C61">
+        <v>7</v>
+      </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="1"/>

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3DA6D0E-44DF-4F2B-A160-00EF4EB062B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CE0CF9-0B41-4C0D-88F3-EBED12B1E776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>Date</t>
   </si>
@@ -243,6 +243,9 @@
   </si>
   <si>
     <t>final präsentation</t>
+  </si>
+  <si>
+    <t>data science kapitel</t>
   </si>
 </sst>
 </file>
@@ -604,7 +607,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>105</v>
+        <v>107.5</v>
       </c>
       <c r="Q2" t="s">
         <v>26</v>
@@ -628,7 +631,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>1.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -657,7 +660,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>15</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -675,7 +678,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>9.545454545454545</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -1284,7 +1287,15 @@
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" s="1"/>
+      <c r="A62" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B62" t="s">
+        <v>69</v>
+      </c>
+      <c r="C62">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="1"/>

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CE0CF9-0B41-4C0D-88F3-EBED12B1E776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CE4AED-2A59-4E5B-B95C-4D86291386C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>Date</t>
   </si>
@@ -246,6 +246,9 @@
   </si>
   <si>
     <t>data science kapitel</t>
+  </si>
+  <si>
+    <t>methodology + implementation</t>
   </si>
 </sst>
 </file>
@@ -607,7 +610,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>107.5</v>
+        <v>111</v>
       </c>
       <c r="Q2" t="s">
         <v>26</v>
@@ -631,7 +634,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>0.7142857142857143</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -660,7 +663,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>12.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -678,7 +681,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>17.5</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -1298,7 +1301,15 @@
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63" s="1"/>
+      <c r="A63" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B63" t="s">
+        <v>70</v>
+      </c>
+      <c r="C63">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="1"/>

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CE4AED-2A59-4E5B-B95C-4D86291386C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01326ED6-1833-411C-802B-DA5A2F887014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t>Date</t>
   </si>
@@ -249,6 +249,9 @@
   </si>
   <si>
     <t>methodology + implementation</t>
+  </si>
+  <si>
+    <t>report improvments</t>
   </si>
 </sst>
 </file>
@@ -610,7 +613,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="Q2" t="s">
         <v>26</v>
@@ -634,7 +637,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>0.5714285714285714</v>
+        <v>0.42857142857142855</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -663,7 +666,7 @@
       </c>
       <c r="R5">
         <f>R2-H2</f>
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -681,7 +684,7 @@
       </c>
       <c r="R6">
         <f ca="1">R5/R3</f>
-        <v>15.75</v>
+        <v>4.666666666666667</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -1312,7 +1315,15 @@
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64" s="1"/>
+      <c r="A64" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B64" t="s">
+        <v>71</v>
+      </c>
+      <c r="C64">
+        <v>7</v>
+      </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>

--- a/timesheets/Dominik.xlsx
+++ b/timesheets/Dominik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01326ED6-1833-411C-802B-DA5A2F887014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDDA4FAD-0EB8-4841-A052-B0C5088D26FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4570" yWindow="1630" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>Date</t>
   </si>
@@ -125,12 +125,6 @@
     <t>End Datum</t>
   </si>
   <si>
-    <t>Need Hours</t>
-  </si>
-  <si>
-    <t>Need per week</t>
-  </si>
-  <si>
     <t xml:space="preserve">meeting with </t>
   </si>
   <si>
@@ -252,6 +246,9 @@
   </si>
   <si>
     <t>report improvments</t>
+  </si>
+  <si>
+    <t>final abgaben</t>
   </si>
 </sst>
 </file>
@@ -613,7 +610,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>118</v>
+        <v>120.5</v>
       </c>
       <c r="Q2" t="s">
         <v>26</v>
@@ -637,7 +634,7 @@
       </c>
       <c r="R3" s="3">
         <f ca="1">(R1 - TODAY()) / 7</f>
-        <v>0.42857142857142855</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -661,13 +658,6 @@
       <c r="C5">
         <v>1.5</v>
       </c>
-      <c r="Q5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R5">
-        <f>R2-H2</f>
-        <v>2</v>
-      </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
@@ -679,13 +669,6 @@
       <c r="C6">
         <v>0.75</v>
       </c>
-      <c r="Q6" t="s">
-        <v>30</v>
-      </c>
-      <c r="R6">
-        <f ca="1">R5/R3</f>
-        <v>4.666666666666667</v>
-      </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
@@ -879,7 +862,7 @@
         <v>46125</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C24">
         <v>0.75</v>
@@ -890,7 +873,7 @@
         <v>46125</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C25">
         <v>0.5</v>
@@ -901,7 +884,7 @@
         <v>46128</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C26">
         <v>1.5</v>
@@ -912,7 +895,7 @@
         <v>46129</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C27">
         <v>0.5</v>
@@ -923,7 +906,7 @@
         <v>46130</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C28">
         <v>3.25</v>
@@ -934,7 +917,7 @@
         <v>46130</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -945,7 +928,7 @@
         <v>46131</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C30">
         <v>0.75</v>
@@ -956,7 +939,7 @@
         <v>46132</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -967,7 +950,7 @@
         <v>46132</v>
       </c>
       <c r="B32" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C32">
         <v>0.5</v>
@@ -978,7 +961,7 @@
         <v>46133</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C33">
         <v>3.25</v>
@@ -989,7 +972,7 @@
         <v>46133</v>
       </c>
       <c r="B34" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C34">
         <v>1.5</v>
@@ -1000,7 +983,7 @@
         <v>46134</v>
       </c>
       <c r="B35" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C35">
         <v>1.25</v>
@@ -1011,7 +994,7 @@
         <v>46135</v>
       </c>
       <c r="B36" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C36">
         <v>2.5</v>
@@ -1022,7 +1005,7 @@
         <v>46142</v>
       </c>
       <c r="B37" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C37">
         <v>1.25</v>
@@ -1033,7 +1016,7 @@
         <v>46145</v>
       </c>
       <c r="B38" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -1044,7 +1027,7 @@
         <v>46145</v>
       </c>
       <c r="B39" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C39">
         <v>0.5</v>
@@ -1055,7 +1038,7 @@
         <v>46149</v>
       </c>
       <c r="B40" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C40">
         <v>0.5</v>
@@ -1066,7 +1049,7 @@
         <v>46151</v>
       </c>
       <c r="B41" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C41">
         <v>5.5</v>
@@ -1077,7 +1060,7 @@
         <v>46153</v>
       </c>
       <c r="B42" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C42">
         <v>2.5</v>
@@ -1088,7 +1071,7 @@
         <v>46156</v>
       </c>
       <c r="B43" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C43">
         <v>0.25</v>
@@ -1099,7 +1082,7 @@
         <v>46161</v>
       </c>
       <c r="B44" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C44">
         <v>2</v>
@@ -1110,7 +1093,7 @@
         <v>46163</v>
       </c>
       <c r="B45" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -1121,7 +1104,7 @@
         <v>46167</v>
       </c>
       <c r="B46" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C46">
         <v>2</v>
@@ -1132,7 +1115,7 @@
         <v>46168</v>
       </c>
       <c r="B47" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C47">
         <v>3</v>
@@ -1143,7 +1126,7 @@
         <v>46169</v>
       </c>
       <c r="B48" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C48">
         <v>2</v>
@@ -1154,7 +1137,7 @@
         <v>46170</v>
       </c>
       <c r="B49" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C49">
         <v>1.5</v>
@@ -1165,7 +1148,7 @@
         <v>46172</v>
       </c>
       <c r="B50" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -1176,7 +1159,7 @@
         <v>46172</v>
       </c>
       <c r="B51" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C51">
         <v>0.75</v>
@@ -1187,7 +1170,7 @@
         <v>46172</v>
       </c>
       <c r="B52" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C52">
         <v>3</v>
@@ -1198,7 +1181,7 @@
         <v>46173</v>
       </c>
       <c r="B53" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C53">
         <v>4</v>
@@ -1209,7 +1192,7 @@
         <v>46174</v>
       </c>
       <c r="B54" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -1220,7 +1203,7 @@
         <v>46177</v>
       </c>
       <c r="B55" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C55">
         <v>0.75</v>
@@ -1231,7 +1214,7 @@
         <v>46180</v>
       </c>
       <c r="B56" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C56">
         <v>1.5</v>
@@ -1242,7 +1225,7 @@
         <v>46184</v>
       </c>
       <c r="B57" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -1253,7 +1236,7 @@
         <v>46186</v>
       </c>
       <c r="B58" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C58">
         <v>4</v>
@@ -1264,7 +1247,7 @@
         <v>46190</v>
       </c>
       <c r="B59" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -1275,7 +1258,7 @@
         <v>46190</v>
       </c>
       <c r="B60" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C60">
         <v>3</v>
@@ -1286,7 +1269,7 @@
         <v>46191</v>
       </c>
       <c r="B61" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C61">
         <v>7</v>
@@ -1297,7 +1280,7 @@
         <v>46196</v>
       </c>
       <c r="B62" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C62">
         <v>2.5</v>
@@ -1308,7 +1291,7 @@
         <v>46197</v>
       </c>
       <c r="B63" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C63">
         <v>3.5</v>
@@ -1319,46 +1302,54 @@
         <v>46198</v>
       </c>
       <c r="B64" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C64">
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A65" s="1"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B65" t="s">
+        <v>70</v>
+      </c>
+      <c r="C65">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="1"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="1"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="1"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="1"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="1"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="1"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="1"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="1"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="1"/>
     </row>
   </sheetData>
